--- a/Pulse Generator_R01.xlsx
+++ b/Pulse Generator_R01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10 - Zigunov\02 - Projects\2025 - SAFS Self-Aligned Focusing Schlieren\03 - Laser Diode Driver UCSB\SAFS_SIV_Laser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10E354C8-8AC0-4E81-9530-0DFEAC164F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87BEC0E8-09A5-43CE-BAAB-78E77C943CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{7947FB3E-6B0A-4175-8A21-692621A5A3F6}"/>
   </bookViews>
@@ -35,58 +35,6 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Fernando Zigunov</author>
-  </authors>
-  <commentList>
-    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{6B0C9B4C-CE8D-4E75-A725-3B6C04209B0D}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Buy more for LED too</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{B62069C4-F0F0-4F79-B239-6D82214B1F6B}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Buy more for case it breaks</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B34" authorId="0" shapeId="0" xr:uid="{EC68993E-1C16-4AAC-8621-E63C9B6C8819}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Buy 10</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
@@ -313,7 +261,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -336,22 +284,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -361,12 +295,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -431,8 +359,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -748,7 +676,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62D38096-62FF-4B3A-B455-132413603466}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62D38096-62FF-4B3A-B455-132413603466}">
   <dimension ref="A1:E46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -821,7 +749,7 @@
         <v>15.48</v>
       </c>
       <c r="D4" s="2">
-        <f t="shared" ref="D4:D25" si="1">C4*B4</f>
+        <f t="shared" ref="D4:D10" si="1">C4*B4</f>
         <v>30.96</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -832,7 +760,7 @@
       <c r="A5" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="9">
         <v>1</v>
       </c>
       <c r="C5" s="2">
@@ -850,7 +778,7 @@
       <c r="A6" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="9">
         <v>1</v>
       </c>
       <c r="C6" s="2">
@@ -947,7 +875,7 @@
         <v>0.1</v>
       </c>
       <c r="D11" s="2">
-        <f>C11*B11</f>
+        <f t="shared" ref="D11:D27" si="2">C11*B11</f>
         <v>0.1</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -965,7 +893,7 @@
         <v>1.58</v>
       </c>
       <c r="D12" s="2">
-        <f>C12*B12</f>
+        <f t="shared" si="2"/>
         <v>1.58</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -983,7 +911,7 @@
         <v>1.58</v>
       </c>
       <c r="D13" s="2">
-        <f>C13*B13</f>
+        <f t="shared" si="2"/>
         <v>1.58</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -1001,7 +929,7 @@
         <v>0.08</v>
       </c>
       <c r="D14" s="2">
-        <f>C14*B14</f>
+        <f t="shared" si="2"/>
         <v>0.08</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -1019,7 +947,7 @@
         <v>0.71</v>
       </c>
       <c r="D15" s="2">
-        <f>C15*B15</f>
+        <f t="shared" si="2"/>
         <v>0.71</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -1037,7 +965,7 @@
         <v>2.85</v>
       </c>
       <c r="D16" s="2">
-        <f>C16*B16</f>
+        <f t="shared" si="2"/>
         <v>2.85</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -1055,7 +983,7 @@
         <v>1.89</v>
       </c>
       <c r="D17" s="2">
-        <f>C17*B17</f>
+        <f t="shared" si="2"/>
         <v>3.78</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -1073,7 +1001,7 @@
         <v>1</v>
       </c>
       <c r="D18" s="2">
-        <f>C18*B18</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -1091,7 +1019,7 @@
         <v>0.15</v>
       </c>
       <c r="D19" s="2">
-        <f>C19*B19</f>
+        <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
       <c r="E19" s="1" t="s">
@@ -1109,7 +1037,7 @@
         <v>7.69</v>
       </c>
       <c r="D20" s="2">
-        <f>C20*B20</f>
+        <f t="shared" si="2"/>
         <v>7.69</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -1127,7 +1055,7 @@
         <v>24.95</v>
       </c>
       <c r="D21" s="2">
-        <f>C21*B21</f>
+        <f t="shared" si="2"/>
         <v>24.95</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -1145,7 +1073,7 @@
         <v>0.38</v>
       </c>
       <c r="D22" s="2">
-        <f>C22*B22</f>
+        <f t="shared" si="2"/>
         <v>0.38</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -1163,7 +1091,7 @@
         <v>2.35</v>
       </c>
       <c r="D23" s="2">
-        <f>C23*B23</f>
+        <f t="shared" si="2"/>
         <v>2.35</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -1181,7 +1109,7 @@
         <v>1.8</v>
       </c>
       <c r="D24" s="2">
-        <f>C24*B24</f>
+        <f t="shared" si="2"/>
         <v>1.8</v>
       </c>
       <c r="E24" s="7" t="s">
@@ -1199,7 +1127,7 @@
         <v>1.58</v>
       </c>
       <c r="D25" s="2">
-        <f>C25*B25</f>
+        <f t="shared" si="2"/>
         <v>3.16</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -1217,7 +1145,7 @@
         <v>0.38</v>
       </c>
       <c r="D26" s="2">
-        <f>C26*B26</f>
+        <f t="shared" si="2"/>
         <v>1.9</v>
       </c>
       <c r="E26" s="1" t="s">
@@ -1235,7 +1163,7 @@
         <v>0.1</v>
       </c>
       <c r="D27" s="2">
-        <f>C27*B27</f>
+        <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -1253,10 +1181,10 @@
         <v>0.76</v>
       </c>
       <c r="D28" s="2">
-        <f t="shared" ref="D28:D34" si="2">C28*B28</f>
+        <f t="shared" ref="D28:D34" si="3">C28*B28</f>
         <v>0.76</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="8" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1271,7 +1199,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="D29" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.1399999999999999</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -1289,7 +1217,7 @@
         <v>0.1</v>
       </c>
       <c r="D30" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -1307,7 +1235,7 @@
         <v>0.15</v>
       </c>
       <c r="D31" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="E31" s="1" t="s">
@@ -1354,14 +1282,14 @@
       <c r="A34" t="s">
         <v>71</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B34" s="9">
         <v>4</v>
       </c>
       <c r="C34" s="2">
         <v>13.6</v>
       </c>
       <c r="D34" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>54.4</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -1437,6 +1365,5 @@
     <hyperlink ref="E34" r:id="rId9" xr:uid="{F8007675-54B2-473F-A6FD-49ACD21008C1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId10"/>
 </worksheet>
 </file>